--- a/templates/Ранжирование.xlsx
+++ b/templates/Ранжирование.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Public\bnk-diplom-abiturient-system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590235DB-E9E1-4ED0-83BF-1EA695ED7E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C345E98C-9AC3-4B5A-B41C-5129D81D55EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="540" windowWidth="29040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -401,10 +401,13 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/templates/Ранжирование.xlsx
+++ b/templates/Ранжирование.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Public\bnk-diplom-abiturient-system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C345E98C-9AC3-4B5A-B41C-5129D81D55EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B8933D-3910-4699-8E8E-7A5F7491E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="540" windowWidth="29040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -402,11 +402,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
     <col min="10" max="10" width="19.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -463,42 +463,12 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/Ранжирование.xlsx
+++ b/templates/Ранжирование.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Public\bnk-diplom-abiturient-system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B8933D-3910-4699-8E8E-7A5F7491E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1655E1F1-E339-442F-8428-083DA39D8477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="540" windowWidth="29040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>№</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Телефон</t>
   </si>
   <si>
-    <t>Наждается в общежитии</t>
-  </si>
-  <si>
     <t>Код + Название специальности</t>
+  </si>
+  <si>
+    <t>Нуждается в общежитии</t>
+  </si>
+  <si>
+    <t>ГАПОУ «Бугурусланский нефтяной колледж» г. Бугуруслана. Ранжирование на (дата) по</t>
   </si>
 </sst>
 </file>
@@ -84,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -107,15 +110,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -404,7 +419,10 @@
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
     <col min="2" max="2" width="39.85546875" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32.5703125" customWidth="1"/>
     <col min="10" max="10" width="19.7109375" customWidth="1"/>
@@ -412,57 +430,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -471,7 +501,8 @@
       <c r="A5" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
